--- a/stories/arbres/ATOM-REL.CON.003-04.xlsx
+++ b/stories/arbres/ATOM-REL.CON.003-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Maëlle dessine dans le salon avec papa. Adam a posé des crayons en ligne. Les crayons sont verts et oranges. Maëlle passe trop près. Les crayons roulent. Adam a les yeux mouillés. Il est triste. Papa s'approche. Papa dit : tu peux dire pardon. Maëlle dit : pardon, Adam. Papa dit : tu peux proposer un geste. Maëlle ramasse un crayon. Elle le tend. C'est un geste simple. Adam prend le crayon. Il reste un peu triste. Papa dit : la peine reste un peu. Le pardon n'efface pas tout de suite. Adam s'assoit près de papa. Maëlle attend. Plus tard, ils vont au jardin. Adam a fait un chemin de cailloux. Maëlle pose le pied trop vite. Les cailloux bougent. Adam fronce les sourcils. Maëlle dit encore : pardon. Elle propose un geste. Elle replace un caillou. Adam respire. La peine reste un peu. Papa laisse du temps. Au salon, puis au jardin, c'est pareil. Pardon, et un geste. La peine reste un peu.</t>
+          <t>Maëlle dessine dans le salon avec papa. Adam a posé des crayons en ligne. Les crayons sont verts et oranges. Maëlle passe trop près. Les crayons roulent. Adam a les yeux mouillés. Il est triste. Papa s'approche. Tu peux dire pardon. Pardon, Adam. Tu peux proposer un geste. Maëlle ramasse un crayon. Elle le tend. C'est un geste simple. Adam prend le crayon. Il reste un peu triste. La peine reste un peu. Le pardon n'efface pas tout de suite. Adam s'assoit près de papa. Maëlle attend. Plus tard, ils vont au jardin. Adam a fait un chemin de cailloux. Maëlle pose le pied trop vite. Les cailloux bougent. Adam fronce les sourcils. Maëlle dit encore : pardon. Elle propose un geste. Elle replace un caillou. Adam respire. La peine reste un peu. Papa laisse du temps. Au salon, puis au jardin, c'est pareil. Pardon, et un geste. La peine reste un peu.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Maëlle dessine dans le salon avec papa. Adam a posé des crayons en ligne. Les crayons sont verts et oranges. Maëlle passe trop près. Les crayons roulent. Adam a les yeux mouillés. Il est triste. Papa s'approche.
+papa|Tu peux dire pardon.
+enfant-f|Pardon, Adam.
+papa|Tu peux proposer un geste.
+narrateur|Maëlle ramasse un crayon. Elle le tend. C'est un geste simple. Adam prend le crayon. Il reste un peu triste.
+papa|La peine reste un peu.
+narrateur|Le pardon n'efface pas tout de suite. Adam s'assoit près de papa. Maëlle attend. Plus tard, ils vont au jardin. Adam a fait un chemin de cailloux. Maëlle pose le pied trop vite. Les cailloux bougent. Adam fronce les sourcils. Maëlle dit encore : pardon. Elle propose un geste. Elle replace un caillou. Adam respire. La peine reste un peu. Papa laisse du temps. Au salon, puis au jardin, c'est pareil. Pardon, et un geste. La peine reste un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Les crayons d'Adam ont bougé. Que fait Maëlle ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Maëlle a dit pardon. Elle a proposé un geste. La peine reste un peu. Papa est là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1828,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Adam pose un crayon. Maëlle pose un caillou. Papa reste près d'eux.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1995,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2035,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.CON.003-04.xlsx
+++ b/stories/arbres/ATOM-REL.CON.003-04.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,7 @@
 narrateur|Le pardon n'efface pas tout de suite. Adam s'assoit près de papa. Maëlle attend. Plus tard, ils vont au jardin. Adam a fait un chemin de cailloux. Maëlle pose le pied trop vite. Les cailloux bougent. Adam fronce les sourcils. Maëlle dit encore : pardon. Elle propose un geste. Elle replace un caillou. Adam respire. La peine reste un peu. Papa laisse du temps. Au salon, puis au jardin, c'est pareil. Pardon, et un geste. La peine reste un peu.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1505,7 @@
           <t>narrateur|Les crayons d'Adam ont bougé. Que fait Maëlle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1670,6 +1677,7 @@
           <t>narrateur|Maëlle a dit pardon. Elle a proposé un geste. La peine reste un peu. Papa est là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1841,7 @@
           <t>narrateur|Adam pose un crayon. Maëlle pose un caillou. Papa reste près d'eux.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2000,6 +2009,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2018,7 +2028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2042,6 +2052,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2243,6 +2267,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-REL.CON.003-04.xlsx
+++ b/stories/arbres/ATOM-REL.CON.003-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Maëlle dit pardon et propose un geste</t>
+          <t>Le rayon orange et les cailloux</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Victorina fait rouler les crayons de Raphaël. Elle dit pardon et tend un crayon. Au jardin, les cailloux bougent. Encore pardon, encore un geste. La peine reste un peu.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Maëlle dessine dans le salon avec papa. Adam a posé des crayons en ligne. Les crayons sont verts et oranges. Maëlle passe trop près. Les crayons roulent. Adam a les yeux mouillés. Il est triste. Papa s'approche. Tu peux dire pardon. Pardon, Adam. Tu peux proposer un geste. Maëlle ramasse un crayon. Elle le tend. C'est un geste simple. Adam prend le crayon. Il reste un peu triste. La peine reste un peu. Le pardon n'efface pas tout de suite. Adam s'assoit près de papa. Maëlle attend. Plus tard, ils vont au jardin. Adam a fait un chemin de cailloux. Maëlle pose le pied trop vite. Les cailloux bougent. Adam fronce les sourcils. Maëlle dit encore : pardon. Elle propose un geste. Elle replace un caillou. Adam respire. La peine reste un peu. Papa laisse du temps. Au salon, puis au jardin, c'est pareil. Pardon, et un geste. La peine reste un peu.</t>
+          <t>Un rayon orange s'étale sur la table. Il est chaud, tout long. Une mouche tapote la vitre, tout bas. Derrière le verre, le jardin est encore mouillé. Un oiseau saute sur le chemin. Papa taille un crayon vert. Les copeaux sentent le bois neuf. Un crayon orange brille dans le rayon. Sa mine est un peu usée. Dehors, une feuille mouillée colle au gravier. Tu as vu l'oiseau, Victorina ? Oui, papa. Il saute. Raphaël a mis ses crayons en ligne. Ils sont verts et oranges. En ce moment, Victorina s'approche de la table. Elle veut un crayon orange. Les crayons roulent. Ils tapent le bois, un par un. Un crayon vert file vers le bord. Raphaël a les yeux mouillés. Il est triste. Raphaël a de la peine, Victorina. Tu peux dire pardon. Pardon, Raphaël. Tu peux proposer un geste. Victorina ramasse un crayon orange. Il est lisse et un peu chaud. Elle le tend. Je te le rends. Raphaël prend le crayon. Il reste un peu triste. La peine reste un peu. Le pardon n'efface pas tout de suite. Raphaël s'assoit près de papa. Victorina attend, les mains calmes. Raphaël tient le crayon contre sa poitrine. Tu as le temps, Raphaël. Le rayon orange glisse vers le bord. On laisse du temps à Raphaël. Tu attends avec moi ? Oui, papa. La mouche s'est tue. Le rayon orange a bougé un peu. Plus tard, ils vont au jardin. L'herbe sent l'eau. Raphaël a fait un chemin de cailloux. Les cailloux sont gris et ronds. Victorina pose le pied trop vite. Les cailloux bougent. Raphaël fronce les sourcils. Pardon, Raphaël. Je replace un caillou. C'est un geste. Raphaël respire. La peine reste un peu. Tu as dit pardon, encore. Tu as proposé un geste. Bravo, Victorina. C'est du bon travail. Raphaël a encore un peu de peine. C'est normal. L'oiseau est reparti. Les copeaux de crayon restent sur la table.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,16 +1324,77 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Maëlle dessine dans le salon avec papa. Adam a posé des crayons en ligne. Les crayons sont verts et oranges. Maëlle passe trop près. Les crayons roulent. Adam a les yeux mouillés. Il est triste. Papa s'approche.
+          <t>narrateur|Un rayon orange s'étale sur la table.
+narrateur|Il est chaud, tout long.
+narrateur|Une mouche tapote la vitre, tout bas.
+narrateur|Derrière le verre, le jardin est encore mouillé.
+narrateur|Un oiseau saute sur le chemin.
+narrateur|Papa taille un crayon vert.
+narrateur|Les copeaux sentent le bois neuf.
+narrateur|Un crayon orange brille dans le rayon.
+narrateur|Sa mine est un peu usée.
+narrateur|Dehors, une feuille mouillée colle au gravier.
+papa|Tu as vu l'oiseau, Victorina ?
+enfant-f|Oui, papa.
+enfant-f|Il saute.
+papa|Raphaël a mis ses crayons en ligne.
+papa|Ils sont verts et oranges.
+narrateur|En ce moment, Victorina s'approche de la table.
+narrateur|Elle veut un crayon orange.
+narrateur|Les crayons roulent.
+narrateur|Ils tapent le bois, un par un.
+narrateur|Un crayon vert file vers le bord.
+narrateur|Raphaël a les yeux mouillés.
+narrateur|Il est triste.
+papa|Raphaël a de la peine, Victorina.
 papa|Tu peux dire pardon.
-enfant-f|Pardon, Adam.
+enfant-f|Pardon, Raphaël.
 papa|Tu peux proposer un geste.
-narrateur|Maëlle ramasse un crayon. Elle le tend. C'est un geste simple. Adam prend le crayon. Il reste un peu triste.
+narrateur|Victorina ramasse un crayon orange.
+narrateur|Il est lisse et un peu chaud.
+narrateur|Elle le tend.
+enfant-f|Je te le rends.
+narrateur|Raphaël prend le crayon.
+narrateur|Il reste un peu triste.
 papa|La peine reste un peu.
-narrateur|Le pardon n'efface pas tout de suite. Adam s'assoit près de papa. Maëlle attend. Plus tard, ils vont au jardin. Adam a fait un chemin de cailloux. Maëlle pose le pied trop vite. Les cailloux bougent. Adam fronce les sourcils. Maëlle dit encore : pardon. Elle propose un geste. Elle replace un caillou. Adam respire. La peine reste un peu. Papa laisse du temps. Au salon, puis au jardin, c'est pareil. Pardon, et un geste. La peine reste un peu.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+papa|Le pardon n'efface pas tout de suite.
+narrateur|Raphaël s'assoit près de papa.
+narrateur|Victorina attend, les mains calmes.
+narrateur|Raphaël tient le crayon contre sa poitrine.
+papa|Tu as le temps, Raphaël.
+narrateur|Le rayon orange glisse vers le bord.
+papa|On laisse du temps à Raphaël.
+papa|Tu attends avec moi ?
+enfant-f|Oui, papa.
+narrateur|La mouche s'est tue.
+narrateur|Le rayon orange a bougé un peu.
+narrateur|Plus tard, ils vont au jardin.
+narrateur|L'herbe sent l'eau.
+narrateur|Raphaël a fait un chemin de cailloux.
+narrateur|Les cailloux sont gris et ronds.
+narrateur|Victorina pose le pied trop vite.
+narrateur|Les cailloux bougent.
+narrateur|Raphaël fronce les sourcils.
+enfant-f|Pardon, Raphaël.
+enfant-f|Je replace un caillou.
+narrateur|C'est un geste.
+narrateur|Raphaël respire.
+narrateur|La peine reste un peu.
+papa|Tu as dit pardon, encore.
+papa|Tu as proposé un geste.
+papa|Bravo, Victorina.
+papa|C'est du bon travail.
+papa|Raphaël a encore un peu de peine.
+papa|C'est normal.
+narrateur|L'oiseau est reparti.
+narrateur|Les copeaux de crayon restent sur la table.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>mouche_vitre,cailloux</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1346,7 +1419,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Les crayons d'Adam ont bougé. Que fait Maëlle ?</t>
+          <t>Les crayons de Raphaël ont bougé. Que fait Victorina ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1502,7 +1575,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Les crayons d'Adam ont bougé. Que fait Maëlle ?</t>
+          <t>narrateur|Les crayons de Raphaël ont bougé.
+narrateur|Que fait Victorina ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1530,7 +1604,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Maëlle a dit pardon. Elle a proposé un geste. La peine reste un peu. Papa est là.</t>
+          <t>Victorina a dit pardon. Elle a proposé un geste. Elle a tendu un crayon. Bravo, Victorina. C'est du bon travail. La peine de Raphaël reste un peu. J'ai dit pardon. Oui. Et tu as attendu.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1674,7 +1748,15 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Maëlle a dit pardon. Elle a proposé un geste. La peine reste un peu. Papa est là.</t>
+          <t>narrateur|Victorina a dit pardon.
+narrateur|Elle a proposé un geste.
+narrateur|Elle a tendu un crayon.
+papa|Bravo, Victorina.
+papa|C'est du bon travail.
+papa|La peine de Raphaël reste un peu.
+enfant-f|J'ai dit pardon.
+papa|Oui.
+papa|Et tu as attendu.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1702,7 +1784,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Adam pose un crayon. Maëlle pose un caillou. Papa reste près d'eux.</t>
+          <t>Raphaël pose un crayon orange. Victorina pose un caillou gris. On reste près du chemin ? Oui, papa. L'herbe est encore mouillée. La peine reste un peu. Je laisse du temps. Oui. C'est bien. Le rayon orange a quitté la table. La feuille mouillée sèche sur le gravier. On regardera l'oiseau une autre fois. D'accord, papa.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1838,7 +1920,19 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Adam pose un crayon. Maëlle pose un caillou. Papa reste près d'eux.</t>
+          <t>narrateur|Raphaël pose un crayon orange.
+narrateur|Victorina pose un caillou gris.
+papa|On reste près du chemin ?
+enfant-f|Oui, papa.
+papa|L'herbe est encore mouillée.
+papa|La peine reste un peu.
+enfant-f|Je laisse du temps.
+papa|Oui.
+papa|C'est bien.
+narrateur|Le rayon orange a quitté la table.
+narrateur|La feuille mouillée sèche sur le gravier.
+papa|On regardera l'oiseau une autre fois.
+enfant-f|D'accord, papa.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1866,7 +1960,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai dit pardon. J'ai tendu un crayon. Bravo. Tu as fait du bon travail. Un caillou reste chaud de soleil. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2006,7 +2100,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai dit pardon.
+enfant-f|J'ai tendu un crayon.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|Un caillou reste chaud de soleil.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2028,7 +2127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2066,6 +2165,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.CON.003-04.xlsx
+++ b/stories/arbres/ATOM-REL.CON.003-04.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Un rayon orange s'étale sur la table. Il est chaud, tout long. Une mouche tapote la vitre, tout bas. Derrière le verre, le jardin est encore mouillé. Un oiseau saute sur le chemin. Papa taille un crayon vert. Les copeaux sentent le bois neuf. Un crayon orange brille dans le rayon. Sa mine est un peu usée. Dehors, une feuille mouillée colle au gravier. Tu as vu l'oiseau, Victorina ? Oui, papa. Il saute. Raphaël a mis ses crayons en ligne. Ils sont verts et oranges. En ce moment, Victorina s'approche de la table. Elle veut un crayon orange. Les crayons roulent. Ils tapent le bois, un par un. Un crayon vert file vers le bord. Raphaël a les yeux mouillés. Il est triste. Raphaël a de la peine, Victorina. Tu peux dire pardon. Pardon, Raphaël. Tu peux proposer un geste. Victorina ramasse un crayon orange. Il est lisse et un peu chaud. Elle le tend. Je te le rends. Raphaël prend le crayon. Il reste un peu triste. La peine reste un peu. Le pardon n'efface pas tout de suite. Raphaël s'assoit près de papa. Victorina attend, les mains calmes. Raphaël tient le crayon contre sa poitrine. Tu as le temps, Raphaël. Le rayon orange glisse vers le bord. On laisse du temps à Raphaël. Tu attends avec moi ? Oui, papa. La mouche s'est tue. Le rayon orange a bougé un peu. Plus tard, ils vont au jardin. L'herbe sent l'eau. Raphaël a fait un chemin de cailloux. Les cailloux sont gris et ronds. Victorina pose le pied trop vite. Les cailloux bougent. Raphaël fronce les sourcils. Pardon, Raphaël. Je replace un caillou. C'est un geste. Raphaël respire. La peine reste un peu. Tu as dit pardon, encore. Tu as proposé un geste. Bravo, Victorina. C'est du bon travail. Raphaël a encore un peu de peine. C'est normal. L'oiseau est reparti. Les copeaux de crayon restent sur la table.</t>
+          <t>Un rayon orange s'étale sur la table. Il est chaud, tout long. Une mouche tapote la vitre, tout bas. Derrière le verre, le jardin est encore mouillé. Un oiseau saute sur le chemin. Papa taille un crayon vert. Les copeaux sentent le bois neuf. Un crayon orange brille dans le rayon. Sa mine est un peu usée. Dehors, une feuille mouillée colle au gravier. Tu as vu l'oiseau, Victorina ? Oui, papa. Il saute. Raphaël a mis ses crayons en ligne. Ils sont verts et oranges. En ce moment, Victorina s'approche de la table. Elle veut un crayon orange. Les crayons roulent. Ils tapent le bois, un par un. Un crayon vert file vers le bord. Raphaël a les yeux mouillés. Il est triste. Raphaël a de la peine, Victorina. Tu peux dire pardon. Pardon, Raphaël. Tu peux proposer un geste. Victorina ramasse un crayon orange. Il est lisse et un peu chaud. Elle le tend. Je te le rends. Raphaël prend le crayon. Il reste un peu triste. La peine reste un peu. Le pardon n'efface pas tout de suite. Raphaël s'assoit près de papa. Victorina attend, les mains calmes. Raphaël tient le crayon contre sa poitrine. Tu as le temps, Raphaël. Le rayon orange glisse vers le bord. On laisse du temps à Raphaël. Tu attends avec moi ? Oui, papa. La mouche s'est tue. Le rayon orange a bougé un peu. Plus tard, ils vont au jardin. L'herbe sent l'eau. Raphaël a fait un chemin de cailloux. Les cailloux sont gris et ronds. Victorina pose le pied trop vite. Les cailloux bougent. Raphaël fronce les sourcils. Pardon, Raphaël. Je replace un caillou. C'est un geste. Raphaël respire. La peine reste un peu. Tu as dit pardon, encore. Tu as proposé un geste. Bravo, Victorina. Raphaël a encore un peu de peine. C'est normal. L'oiseau est reparti. Les copeaux de crayon restent sur la table.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maëlle dessine dans le salon avec papa. Adam a posé des crayons en ligne. Les crayons sont verts et oranges. Maëlle passe trop près. Les crayons roulent. Adam a les yeux mouillés. Il est triste. Papa s'approche. Papa dit : tu peux dire &lt;emphasis level="moderate"&gt;pardon&lt;/emphasis&gt;. Maëlle dit : pardon, Adam. Papa dit : tu peux proposer un geste. Maëlle ramasse un crayon. Elle le tend. C'est un geste simple. Adam prend le crayon. Il reste un peu triste. Papa dit : la peine reste un peu. Le pardon n'efface pas tout de suite. Adam s'assoit près de papa. Maëlle attend. Plus tard, ils vont au jardin. Adam a fait un chemin de cailloux. Maëlle pose le pied trop vite. Les cailloux bougent. Adam fronce les sourcils. Maëlle dit encore : pardon. Elle propose un geste. Elle replace un caillou. Adam respire. La peine reste un peu. Papa laisse du temps. Au salon, puis au jardin, c'est pareil. Pardon, et un geste. La peine reste un peu.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un rayon orange s'étale sur la table. Il est chaud, tout long. Une mouche tapote la vitre, tout bas. Derrière le verre, le jardin est encore mouillé. Un oiseau saute sur le chemin. Papa taille un crayon vert. Les copeaux sentent le bois neuf. Un crayon orange brille dans le rayon. Sa mine est un peu usée. Dehors, une feuille mouillée colle au gravier. Tu as vu l'oiseau, Victorina ? Oui, papa. Il saute. Raphaël a mis ses crayons en ligne. Ils sont verts et oranges. En ce moment, Victorina s'approche de la table. Elle veut un crayon orange. Les crayons roulent. Ils tapent le bois, un par un. Un crayon vert file vers le bord. Raphaël a les yeux mouillés. Il est triste. Raphaël a de la peine, Victorina. Tu peux dire pardon. Pardon, Raphaël. Tu peux proposer un geste. Victorina ramasse un crayon orange. Il est lisse et un peu chaud. Elle le tend. Je te le rends. Raphaël prend le crayon. Il reste un peu triste. La peine reste un peu. Le pardon n'efface pas tout de suite. Raphaël s'assoit près de papa. Victorina attend, les mains calmes. Raphaël tient le crayon contre sa poitrine. Tu as le temps, Raphaël. Le rayon orange glisse vers le bord. On laisse du temps à Raphaël. Tu attends avec moi ? Oui, papa. La mouche s'est tue. Le rayon orange a bougé un peu. Plus tard, ils vont au jardin. L'herbe sent l'eau. Raphaël a fait un chemin de cailloux. Les cailloux sont gris et ronds. Victorina pose le pied trop vite. Les cailloux bougent. Raphaël fronce les sourcils. Pardon, Raphaël. Je replace un caillou. C'est un geste. Raphaël respire. La peine reste un peu. Tu as dit pardon, encore. Tu as proposé un geste. Bravo, Victorina. Raphaël a encore un peu de peine. C'est normal. L'oiseau est reparti. Les copeaux de crayon restent sur la table.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1383,7 +1383,6 @@
 papa|Tu as dit pardon, encore.
 papa|Tu as proposé un geste.
 papa|Bravo, Victorina.
-papa|C'est du bon travail.
 papa|Raphaël a encore un peu de peine.
 papa|C'est normal.
 narrateur|L'oiseau est reparti.
@@ -1424,7 +1423,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Les crayons d'Adam ont bougé. Que fait Maëlle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les crayons de Raphaël ont bougé. Que fait Victorina ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1579,7 +1578,6 @@
 narrateur|Que fait Victorina ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1604,12 +1602,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Victorina a dit pardon. Elle a proposé un geste. Elle a tendu un crayon. Bravo, Victorina. C'est du bon travail. La peine de Raphaël reste un peu. J'ai dit pardon. Oui. Et tu as attendu.</t>
+          <t>Victorina a dit pardon. Elle a proposé un geste. Elle a tendu un crayon. Bravo, Victorina. La peine de Raphaël reste un peu. J'ai dit pardon. Oui. Et tu as attendu.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maëlle a dit &lt;emphasis level="moderate"&gt;pardon&lt;/emphasis&gt;. Elle a proposé un geste. La peine reste un peu. Papa est là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina a dit pardon. Elle a proposé un geste. Elle a tendu un crayon. Bravo, Victorina. La peine de Raphaël reste un peu. J'ai dit pardon. Oui. Et tu as attendu.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1752,14 +1750,12 @@
 narrateur|Elle a proposé un geste.
 narrateur|Elle a tendu un crayon.
 papa|Bravo, Victorina.
-papa|C'est du bon travail.
 papa|La peine de Raphaël reste un peu.
 enfant-f|J'ai dit pardon.
 papa|Oui.
 papa|Et tu as attendu.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1789,7 +1785,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Adam pose un crayon. Maëlle pose un caillou. Papa reste près d'eux.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël pose un crayon orange. Victorina pose un caillou gris. On reste près du chemin ? Oui, papa. L'herbe est encore mouillée. La peine reste un peu. Je laisse du temps. Oui. C'est bien. Le rayon orange a quitté la table. La feuille mouillée sèche sur le gravier. On regardera l'oiseau une autre fois. D'accord, papa.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1935,7 +1931,6 @@
 enfant-f|D'accord, papa.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1960,12 +1955,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai dit pardon. J'ai tendu un crayon. Bravo. Tu as fait du bon travail. Un caillou reste chaud de soleil. L'histoire est finie.</t>
+          <t>J'ai dit pardon. J'ai tendu un crayon. Bravo. Un caillou reste chaud de soleil.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai dit pardon. J'ai tendu un crayon. Bravo. Un caillou reste chaud de soleil.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2103,12 +2098,9 @@
           <t>enfant-f|J'ai dit pardon.
 enfant-f|J'ai tendu un crayon.
 papa|Bravo.
-papa|Tu as fait du bon travail.
-narrateur|Un caillou reste chaud de soleil.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Un caillou reste chaud de soleil.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2127,7 +2119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2172,6 +2164,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.CON.003-04.xlsx
+++ b/stories/arbres/ATOM-REL.CON.003-04.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Maëlle, papa, Adam</t>
+          <t>Victorina, Raphaël, papa</t>
         </is>
       </c>
     </row>
